--- a/evac_by_zip/evac_by_zip_2026-08-16.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-16.xlsx
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -1942,16 +1942,16 @@
         </is>
       </c>
       <c r="B41" s="14" t="n">
-        <v>3285</v>
+        <v>3251</v>
       </c>
       <c r="C41" s="14" t="n">
-        <v>2767</v>
+        <v>2774</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>7270</v>
+        <v>7236</v>
       </c>
     </row>
     <row r="42">
@@ -1964,10 +1964,10 @@
         <v>179</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E42" s="16" t="n">
         <v>283</v>
@@ -1980,16 +1980,16 @@
         </is>
       </c>
       <c r="B43" s="18" t="n">
-        <v>3464</v>
+        <v>3430</v>
       </c>
       <c r="C43" s="18" t="n">
-        <v>2824</v>
+        <v>2834</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>7553</v>
+        <v>7519</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G339"/>
+  <dimension ref="A1:G338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B132" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-S</t>
+          <t>US-OR-CRO-CRR-4SB-G</t>
         </is>
       </c>
       <c r="C132" s="22" t="inlineStr">
@@ -6606,11 +6606,11 @@
       </c>
       <c r="F132" s="21" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G132" s="21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B133" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-G</t>
+          <t>US-OR-CRO-CRR-4SK-A</t>
         </is>
       </c>
       <c r="C133" s="22" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G133" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="B134" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-A</t>
+          <t>US-OR-CRO-CRR-4S-E</t>
         </is>
       </c>
       <c r="C134" s="22" t="inlineStr">
@@ -6676,151 +6676,151 @@
       </c>
       <c r="F134" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G134" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="21" t="inlineStr">
+      <c r="A135" s="23" t="inlineStr">
         <is>
           <t>97754</t>
         </is>
       </c>
-      <c r="B135" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-I</t>
-        </is>
-      </c>
-      <c r="C135" s="22" t="inlineStr">
+      <c r="B135" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-D</t>
+        </is>
+      </c>
+      <c r="C135" s="24" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D135" s="22" t="inlineStr">
+      <c r="D135" s="24" t="inlineStr">
         <is>
           <t>Crook, Wheeler</t>
         </is>
       </c>
-      <c r="E135" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F135" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G135" s="21" t="n">
-        <v>2</v>
+      <c r="E135" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F135" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="21" t="inlineStr">
+      <c r="A136" s="23" t="inlineStr">
         <is>
           <t>97754</t>
         </is>
       </c>
-      <c r="B136" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-M</t>
-        </is>
-      </c>
-      <c r="C136" s="22" t="inlineStr">
+      <c r="B136" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SK-C</t>
+        </is>
+      </c>
+      <c r="C136" s="24" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D136" s="22" t="inlineStr">
+      <c r="D136" s="24" t="inlineStr">
         <is>
           <t>Crook, Wheeler</t>
         </is>
       </c>
-      <c r="E136" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F136" s="21" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G136" s="21" t="n">
-        <v>1</v>
+      <c r="E136" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F136" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G136" s="23" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="21" t="inlineStr">
+      <c r="A137" s="23" t="inlineStr">
         <is>
           <t>97754</t>
         </is>
       </c>
-      <c r="B137" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-I</t>
-        </is>
-      </c>
-      <c r="C137" s="22" t="inlineStr">
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-8S-O</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D137" s="22" t="inlineStr">
+      <c r="D137" s="24" t="inlineStr">
         <is>
           <t>Crook, Wheeler</t>
         </is>
       </c>
-      <c r="E137" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F137" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G137" s="21" t="n">
-        <v>1</v>
+      <c r="E137" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F137" s="23" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="G137" s="23" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="21" t="inlineStr">
+      <c r="A138" s="23" t="inlineStr">
         <is>
           <t>97754</t>
         </is>
       </c>
-      <c r="B138" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-E</t>
-        </is>
-      </c>
-      <c r="C138" s="22" t="inlineStr">
+      <c r="B138" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-L</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D138" s="22" t="inlineStr">
+      <c r="D138" s="24" t="inlineStr">
         <is>
           <t>Crook, Wheeler</t>
         </is>
       </c>
-      <c r="E138" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F138" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G138" s="21" t="n">
-        <v>1</v>
+      <c r="E138" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F138" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G138" s="23" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="139">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-D</t>
+          <t>US-OR-CRO-CRR-4SB-I</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="G139" s="23" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-C</t>
+          <t>US-OR-CRO-CRR-4S-K</t>
         </is>
       </c>
       <c r="C140" s="24" t="inlineStr">
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="G140" s="23" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-O</t>
+          <t>US-OR-CRO-CRR-4SC-B</t>
         </is>
       </c>
       <c r="C141" s="24" t="inlineStr">
@@ -6921,11 +6921,11 @@
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G141" s="23" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-L</t>
+          <t>US-OR-CRO-CRR-4SB-C</t>
         </is>
       </c>
       <c r="C142" s="24" t="inlineStr">
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="G142" s="23" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-I</t>
+          <t>US-OR-CRO-CRR-8S-T</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="G143" s="23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="B144" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-K</t>
+          <t>US-OR-CRO-CRR-4S-F</t>
         </is>
       </c>
       <c r="C144" s="24" t="inlineStr">
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="G144" s="23" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B145" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC-B</t>
+          <t>US-OR-CRO-CRR-4SB-J</t>
         </is>
       </c>
       <c r="C145" s="24" t="inlineStr">
@@ -7061,11 +7061,11 @@
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G145" s="23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-C</t>
+          <t>US-OR-CRO-CRR-8S-S</t>
         </is>
       </c>
       <c r="C146" s="24" t="inlineStr">
@@ -7096,11 +7096,11 @@
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="G146" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B147" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-T</t>
+          <t>US-OR-CRO-CRR-4S-N</t>
         </is>
       </c>
       <c r="C147" s="24" t="inlineStr">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="G147" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="B148" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-F</t>
+          <t>US-OR-CRO-CRR-4S-I</t>
         </is>
       </c>
       <c r="C148" s="24" t="inlineStr">
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="G148" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-J</t>
+          <t>US-OR-CRO-CRR-4SK-B</t>
         </is>
       </c>
       <c r="C149" s="24" t="inlineStr">
@@ -7201,11 +7201,11 @@
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B150" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-N</t>
+          <t>US-OR-CRO-CRR-1S-Q</t>
         </is>
       </c>
       <c r="C150" s="24" t="inlineStr">
@@ -7236,11 +7236,11 @@
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-B</t>
+          <t>US-OR-CRO-CRR-8S-M</t>
         </is>
       </c>
       <c r="C151" s="24" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-Q</t>
+          <t>US-OR-CRO-CRR-8S-I</t>
         </is>
       </c>
       <c r="C152" s="24" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G152" s="23" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B155" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-M</t>
+          <t>US-OR-CRO-CRR-4S-J</t>
         </is>
       </c>
       <c r="C155" s="26" t="inlineStr">
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="G155" s="25" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="B156" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-J</t>
+          <t>US-OR-CRO-CRR-1S-J</t>
         </is>
       </c>
       <c r="C156" s="26" t="inlineStr">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="G156" s="25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B157" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-J</t>
+          <t>US-OR-CRO-CRR-1S-K</t>
         </is>
       </c>
       <c r="C157" s="26" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F157" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="G157" s="25" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="B158" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-K</t>
+          <t>US-OR-CRO-CRR-1S-F</t>
         </is>
       </c>
       <c r="C158" s="26" t="inlineStr">
@@ -7516,11 +7516,11 @@
       </c>
       <c r="F158" s="25" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G158" s="25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B159" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-F</t>
+          <t>US-OR-CRO-CRR-8SG-B</t>
         </is>
       </c>
       <c r="C159" s="26" t="inlineStr">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="G159" s="25" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="B160" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SG-B</t>
+          <t>US-OR-CRO-CRR-4SB-D</t>
         </is>
       </c>
       <c r="C160" s="26" t="inlineStr">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="G160" s="25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B161" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-D</t>
+          <t>US-OR-CRO-CRR-1S-M</t>
         </is>
       </c>
       <c r="C161" s="26" t="inlineStr">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G161" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="B162" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-M</t>
+          <t>US-OR-CRO-CRR-4SB-E</t>
         </is>
       </c>
       <c r="C162" s="26" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="B163" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-E</t>
+          <t>US-OR-CRO-CRR-8S-N</t>
         </is>
       </c>
       <c r="C163" s="26" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B164" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-N</t>
+          <t>US-OR-CRO-CRR-1S-N</t>
         </is>
       </c>
       <c r="C164" s="26" t="inlineStr">
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="G164" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B165" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-N</t>
+          <t>US-OR-CRO-CRR-8SG-A</t>
         </is>
       </c>
       <c r="C165" s="26" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B166" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SG-A</t>
+          <t>US-OR-CRO-CRR-8S-E</t>
         </is>
       </c>
       <c r="C166" s="26" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B167" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-E</t>
+          <t>US-OR-CRO-CRR-8S-Q</t>
         </is>
       </c>
       <c r="C167" s="26" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="F167" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="G167" s="25" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="B168" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-Q</t>
+          <t>US-OR-CRO-CRR-8S-G</t>
         </is>
       </c>
       <c r="C168" s="26" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G168" s="25" t="n">
@@ -7874,38 +7874,38 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="25" t="inlineStr">
-        <is>
-          <t>97754</t>
-        </is>
-      </c>
-      <c r="B169" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-G</t>
-        </is>
-      </c>
-      <c r="C169" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D169" s="26" t="inlineStr">
-        <is>
-          <t>Crook, Wheeler</t>
-        </is>
-      </c>
-      <c r="E169" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F169" s="25" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="G169" s="25" t="n">
-        <v>1</v>
+      <c r="A169" s="21" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B169" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1396</t>
+        </is>
+      </c>
+      <c r="C169" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D169" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E169" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F169" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G169" s="21" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="170">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="B170" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1396</t>
+          <t>US-OR-KLA-KLA-1381-C</t>
         </is>
       </c>
       <c r="C170" s="22" t="inlineStr">
@@ -7936,11 +7936,11 @@
       </c>
       <c r="F170" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="G170" s="21" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="B171" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-C</t>
+          <t>US-OR-KLA-KLA-1717</t>
         </is>
       </c>
       <c r="C171" s="22" t="inlineStr">
@@ -7971,11 +7971,11 @@
       </c>
       <c r="F171" s="21" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G171" s="21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B172" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1717</t>
+          <t>US-OR-KLA-KLA-1381-B</t>
         </is>
       </c>
       <c r="C172" s="22" t="inlineStr">
@@ -8006,11 +8006,11 @@
       </c>
       <c r="F172" s="21" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G172" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B173" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
+          <t>US-OR-KLA-FHZ-1582</t>
         </is>
       </c>
       <c r="C173" s="22" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="F173" s="21" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G173" s="21" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="B174" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1582</t>
+          <t>US-OR-KLA-KLA-1167</t>
         </is>
       </c>
       <c r="C174" s="22" t="inlineStr">
@@ -8084,38 +8084,38 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="21" t="inlineStr">
+      <c r="A175" s="23" t="inlineStr">
         <is>
           <t>97639</t>
         </is>
       </c>
-      <c r="B175" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1167</t>
-        </is>
-      </c>
-      <c r="C175" s="22" t="inlineStr">
+      <c r="B175" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1386</t>
+        </is>
+      </c>
+      <c r="C175" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D175" s="22" t="inlineStr">
+      <c r="D175" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E175" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F175" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G175" s="21" t="n">
-        <v>1</v>
+      <c r="E175" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F175" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="176">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="B176" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1386</t>
+          <t>US-OR-KLA-KLA-1426</t>
         </is>
       </c>
       <c r="C176" s="24" t="inlineStr">
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="G176" s="23" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="B177" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1426</t>
+          <t>US-OR-KLA-FHZ-1583</t>
         </is>
       </c>
       <c r="C177" s="24" t="inlineStr">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="F177" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B178" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1583</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C178" s="24" t="inlineStr">
@@ -8216,11 +8216,11 @@
       </c>
       <c r="F178" s="23" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B179" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-KLA-KLA-1381-A</t>
         </is>
       </c>
       <c r="C179" s="24" t="inlineStr">
@@ -8251,11 +8251,11 @@
       </c>
       <c r="F179" s="23" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G179" s="23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B180" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-A</t>
+          <t>US-OR-KLA-KLA-1431</t>
         </is>
       </c>
       <c r="C180" s="24" t="inlineStr">
@@ -8286,11 +8286,11 @@
       </c>
       <c r="F180" s="23" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G180" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="B181" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1431</t>
+          <t>US-OR-KLA-KLA-1718-A</t>
         </is>
       </c>
       <c r="C181" s="24" t="inlineStr">
@@ -8321,11 +8321,11 @@
       </c>
       <c r="F181" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="B182" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1718-A</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C182" s="24" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="F182" s="23" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G182" s="23" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B183" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-KLA-KLA-1718-B</t>
         </is>
       </c>
       <c r="C183" s="24" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="F183" s="23" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G183" s="23" t="n">
@@ -8399,38 +8399,38 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="23" t="inlineStr">
+      <c r="A184" s="25" t="inlineStr">
         <is>
           <t>97639</t>
         </is>
       </c>
-      <c r="B184" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1718-B</t>
-        </is>
-      </c>
-      <c r="C184" s="24" t="inlineStr">
+      <c r="B184" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1577</t>
+        </is>
+      </c>
+      <c r="C184" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D184" s="24" t="inlineStr">
+      <c r="D184" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E184" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F184" s="23" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="n">
-        <v>1</v>
+      <c r="E184" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F184" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G184" s="25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="B185" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1577</t>
+          <t>US-OR-KLA-FHZ-1584-A</t>
         </is>
       </c>
       <c r="C185" s="26" t="inlineStr">
@@ -8461,11 +8461,11 @@
       </c>
       <c r="F185" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G185" s="25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="B186" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1584-A</t>
+          <t>US-OR-KLA-KLA-1371</t>
         </is>
       </c>
       <c r="C186" s="26" t="inlineStr">
@@ -8496,11 +8496,11 @@
       </c>
       <c r="F186" s="25" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G186" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="B187" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1371</t>
+          <t>US-OR-KLA-FHZ-1584-B</t>
         </is>
       </c>
       <c r="C187" s="26" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="F187" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G187" s="25" t="n">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="B188" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1584-B</t>
+          <t>US-OR-KLA-FHZ-1585</t>
         </is>
       </c>
       <c r="C188" s="26" t="inlineStr">
@@ -8566,46 +8566,46 @@
       </c>
       <c r="F188" s="25" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G188" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="25" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B189" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1585</t>
-        </is>
-      </c>
-      <c r="C189" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D189" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E189" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F189" s="25" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G189" s="25" t="n">
-        <v>1</v>
+      <c r="A189" s="21" t="inlineStr">
+        <is>
+          <t>97058</t>
+        </is>
+      </c>
+      <c r="B189" s="22" t="inlineStr">
+        <is>
+          <t>WRR</t>
+        </is>
+      </c>
+      <c r="C189" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E189" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F189" s="21" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G189" s="21" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="190">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="B190" s="22" t="inlineStr">
         <is>
-          <t>WRR</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="C190" s="22" t="inlineStr">
@@ -8636,46 +8636,46 @@
       </c>
       <c r="F190" s="21" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G190" s="21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="21" t="inlineStr">
+      <c r="A191" s="23" t="inlineStr">
         <is>
           <t>97058</t>
         </is>
       </c>
-      <c r="B191" s="22" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C191" s="22" t="inlineStr">
+      <c r="B191" s="24" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="C191" s="24" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D191" s="22" t="inlineStr">
+      <c r="D191" s="24" t="inlineStr">
         <is>
           <t>Wasco</t>
         </is>
       </c>
-      <c r="E191" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F191" s="21" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G191" s="21" t="n">
-        <v>1</v>
+      <c r="E191" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F191" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="192">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="B192" s="24" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>PHR</t>
         </is>
       </c>
       <c r="C192" s="24" t="inlineStr">
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="G192" s="23" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="B193" s="24" t="inlineStr">
         <is>
-          <t>PHR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C193" s="24" t="inlineStr">
@@ -8741,46 +8741,46 @@
       </c>
       <c r="F193" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="23" t="inlineStr">
+      <c r="A194" s="25" t="inlineStr">
         <is>
           <t>97058</t>
         </is>
       </c>
-      <c r="B194" s="24" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C194" s="24" t="inlineStr">
+      <c r="B194" s="26" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="C194" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D194" s="24" t="inlineStr">
+      <c r="D194" s="26" t="inlineStr">
         <is>
           <t>Wasco</t>
         </is>
       </c>
-      <c r="E194" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F194" s="23" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G194" s="23" t="n">
-        <v>3</v>
+      <c r="E194" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F194" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G194" s="25" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="195">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="B195" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>UFM</t>
         </is>
       </c>
       <c r="C195" s="26" t="inlineStr">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="G195" s="25" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="196">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="B196" s="26" t="inlineStr">
         <is>
-          <t>UFM</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="C196" s="26" t="inlineStr">
@@ -8846,46 +8846,46 @@
       </c>
       <c r="F196" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="G196" s="25" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="25" t="inlineStr">
-        <is>
-          <t>97058</t>
-        </is>
-      </c>
-      <c r="B197" s="26" t="inlineStr">
-        <is>
-          <t>MCR</t>
-        </is>
-      </c>
-      <c r="C197" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D197" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E197" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F197" s="25" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G197" s="25" t="n">
-        <v>4</v>
+      <c r="A197" s="21" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B197" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406017-A</t>
+        </is>
+      </c>
+      <c r="C197" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D197" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E197" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F197" s="21" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G197" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="198">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="B198" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>US-OR-UMA-UMC-1406053-C</t>
         </is>
       </c>
       <c r="C198" s="22" t="inlineStr">
@@ -8916,11 +8916,11 @@
       </c>
       <c r="F198" s="21" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G198" s="21" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="B199" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406053-C</t>
+          <t>US-OR-UMA-UMC-1406015-D</t>
         </is>
       </c>
       <c r="C199" s="22" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G199" s="21" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="B200" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-D</t>
+          <t>US-OR-UMA-UMC-151-D</t>
         </is>
       </c>
       <c r="C200" s="22" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="F200" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G200" s="21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B201" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-UMA-UMC-153</t>
         </is>
       </c>
       <c r="C201" s="22" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F201" s="21" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G201" s="21" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="B202" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-153</t>
+          <t>US-OR-UMA-UMC-1406015-A</t>
         </is>
       </c>
       <c r="C202" s="22" t="inlineStr">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="F202" s="21" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G202" s="21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="B203" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-A</t>
+          <t>US-OR-UMA-UMC-1406015-C</t>
         </is>
       </c>
       <c r="C203" s="22" t="inlineStr">
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="G203" s="21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="B204" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-UMA-UMC-1406053-B</t>
         </is>
       </c>
       <c r="C204" s="22" t="inlineStr">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="G204" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B205" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
+          <t>US-OR-UMA-UMC-155-B</t>
         </is>
       </c>
       <c r="C205" s="22" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="F205" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G205" s="21" t="n">
@@ -9169,38 +9169,38 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="21" t="inlineStr">
+      <c r="A206" s="23" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B206" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-155-B</t>
-        </is>
-      </c>
-      <c r="C206" s="22" t="inlineStr">
+      <c r="B206" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-E</t>
+        </is>
+      </c>
+      <c r="C206" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D206" s="22" t="inlineStr">
+      <c r="D206" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E206" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F206" s="21" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G206" s="21" t="n">
-        <v>1</v>
+      <c r="E206" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F206" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G206" s="23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="207">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B207" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-E</t>
+          <t>US-OR-UMA-UMC-215-D</t>
         </is>
       </c>
       <c r="C207" s="24" t="inlineStr">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="G207" s="23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="B208" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-D</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C208" s="24" t="inlineStr">
@@ -9266,11 +9266,11 @@
       </c>
       <c r="F208" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G208" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-UMA-UMC-149-B</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
@@ -9301,46 +9301,46 @@
       </c>
       <c r="F209" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="G209" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="23" t="inlineStr">
+      <c r="A210" s="25" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B210" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-149-B</t>
-        </is>
-      </c>
-      <c r="C210" s="24" t="inlineStr">
+      <c r="B210" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-C</t>
+        </is>
+      </c>
+      <c r="C210" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D210" s="24" t="inlineStr">
+      <c r="D210" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E210" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F210" s="23" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="G210" s="23" t="n">
-        <v>1</v>
+      <c r="E210" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F210" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G210" s="25" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="211">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B211" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-C</t>
+          <t>US-OR-UMA-UMC-215-F</t>
         </is>
       </c>
       <c r="C211" s="26" t="inlineStr">
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G211" s="25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B212" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-F</t>
+          <t>US-OR-UMA-UMC-151-G</t>
         </is>
       </c>
       <c r="C212" s="26" t="inlineStr">
@@ -9406,45 +9406,45 @@
       </c>
       <c r="F212" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G212" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="25" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B213" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-151-G</t>
-        </is>
-      </c>
-      <c r="C213" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D213" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E213" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F213" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G213" s="25" t="n">
+      <c r="A213" s="21" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B213" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1713-B</t>
+        </is>
+      </c>
+      <c r="C213" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D213" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E213" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F213" s="21" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G213" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="B214" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-B</t>
+          <t>US-OR-KLA-KLA-1713-A</t>
         </is>
       </c>
       <c r="C214" s="22" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="F214" s="21" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G214" s="21" t="n">
@@ -9484,38 +9484,38 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="21" t="inlineStr">
+      <c r="A215" s="23" t="inlineStr">
         <is>
           <t>97625</t>
         </is>
       </c>
-      <c r="B215" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1713-A</t>
-        </is>
-      </c>
-      <c r="C215" s="22" t="inlineStr">
+      <c r="B215" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1707</t>
+        </is>
+      </c>
+      <c r="C215" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D215" s="22" t="inlineStr">
+      <c r="D215" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E215" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F215" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G215" s="21" t="n">
-        <v>1</v>
+      <c r="E215" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F215" s="23" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="G215" s="23" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="216">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="B216" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1707</t>
+          <t>US-OR-KLA-KLA-1941</t>
         </is>
       </c>
       <c r="C216" s="24" t="inlineStr">
@@ -9546,11 +9546,11 @@
       </c>
       <c r="F216" s="23" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G216" s="23" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="B217" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1941</t>
+          <t>US-OR-KLA-KLA-1956</t>
         </is>
       </c>
       <c r="C217" s="24" t="inlineStr">
@@ -9581,46 +9581,46 @@
       </c>
       <c r="F217" s="23" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G217" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="23" t="inlineStr">
+      <c r="A218" s="25" t="inlineStr">
         <is>
           <t>97625</t>
         </is>
       </c>
-      <c r="B218" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1956</t>
-        </is>
-      </c>
-      <c r="C218" s="24" t="inlineStr">
+      <c r="B218" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2261</t>
+        </is>
+      </c>
+      <c r="C218" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D218" s="24" t="inlineStr">
+      <c r="D218" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E218" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F218" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G218" s="23" t="n">
-        <v>1</v>
+      <c r="E218" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F218" s="25" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G218" s="25" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="219">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="B219" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-KLA-KLA-1946</t>
         </is>
       </c>
       <c r="C219" s="26" t="inlineStr">
@@ -9651,11 +9651,11 @@
       </c>
       <c r="F219" s="25" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G219" s="25" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="B220" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1946</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C220" s="26" t="inlineStr">
@@ -9686,11 +9686,11 @@
       </c>
       <c r="F220" s="25" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G220" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="B221" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1701</t>
+          <t>US-OR-KLA-KLA-1361</t>
         </is>
       </c>
       <c r="C221" s="26" t="inlineStr">
@@ -9729,38 +9729,38 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="25" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B222" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1361</t>
-        </is>
-      </c>
-      <c r="C222" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D222" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E222" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F222" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G222" s="25" t="n">
-        <v>1</v>
+      <c r="A222" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B222" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140618N</t>
+        </is>
+      </c>
+      <c r="C222" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D222" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E222" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F222" s="21" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G222" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="223">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="B223" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140618N</t>
+          <t>US-OR-UNI-UCO-140624N-B</t>
         </is>
       </c>
       <c r="C223" s="22" t="inlineStr">
@@ -9791,11 +9791,11 @@
       </c>
       <c r="F223" s="21" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G223" s="21" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B224" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
+          <t>US-OR-UNI-UCO-140624S</t>
         </is>
       </c>
       <c r="C224" s="22" t="inlineStr">
@@ -9826,11 +9826,11 @@
       </c>
       <c r="F224" s="21" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="G224" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B225" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624S</t>
+          <t>US-OR-UMA-UMC-1406030-A</t>
         </is>
       </c>
       <c r="C225" s="22" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F225" s="21" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G225" s="21" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="B226" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>US-OR-UMA-UMC-1406024A</t>
         </is>
       </c>
       <c r="C226" s="22" t="inlineStr">
@@ -9904,37 +9904,37 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="21" t="inlineStr">
+      <c r="A227" s="25" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B227" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C227" s="22" t="inlineStr">
+      <c r="B227" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1497</t>
+        </is>
+      </c>
+      <c r="C227" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D227" s="22" t="inlineStr">
+      <c r="D227" s="26" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E227" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F227" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G227" s="21" t="n">
+      <c r="E227" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F227" s="25" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="G227" s="25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="B228" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1497</t>
+          <t>US-OR-UNI-UCO-1505</t>
         </is>
       </c>
       <c r="C228" s="26" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="F228" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G228" s="25" t="n">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="B229" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1505</t>
+          <t>US-OR-UNI-UCO-1513</t>
         </is>
       </c>
       <c r="C229" s="26" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="F229" s="25" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G229" s="25" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="B230" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1513</t>
+          <t>US-OR-UNI-UCO-1495</t>
         </is>
       </c>
       <c r="C230" s="26" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="F230" s="25" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G230" s="25" t="n">
@@ -10044,38 +10044,38 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B231" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1495</t>
-        </is>
-      </c>
-      <c r="C231" s="26" t="inlineStr">
+      <c r="A231" s="21" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B231" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-123-B</t>
+        </is>
+      </c>
+      <c r="C231" s="22" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D231" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E231" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F231" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G231" s="25" t="n">
-        <v>1</v>
+      <c r="D231" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E231" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F231" s="21" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G231" s="21" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="232">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="B232" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-B</t>
+          <t>US-OR-UMA-UMC-121-B</t>
         </is>
       </c>
       <c r="C232" s="22" t="inlineStr">
@@ -10106,207 +10106,207 @@
       </c>
       <c r="F232" s="21" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G232" s="21" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="21" t="inlineStr">
+      <c r="A233" s="23" t="inlineStr">
         <is>
           <t>97862</t>
         </is>
       </c>
-      <c r="B233" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C233" s="22" t="inlineStr">
+      <c r="B233" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406025-B</t>
+        </is>
+      </c>
+      <c r="C233" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D233" s="22" t="inlineStr">
+      <c r="D233" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E233" s="21" t="inlineStr">
+      <c r="E233" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F233" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G233" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="21" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B234" s="22" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C234" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D234" s="22" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E234" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F233" s="21" t="inlineStr">
+      <c r="F234" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G234" s="21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="25" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B235" s="26" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C235" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D235" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E235" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F235" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G235" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="21" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B236" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406015-D</t>
+        </is>
+      </c>
+      <c r="C236" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D236" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E236" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F236" s="21" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G233" s="21" t="n">
+      <c r="G236" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="23" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B234" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
-        </is>
-      </c>
-      <c r="C234" s="24" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="23" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B237" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C237" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D234" s="24" t="inlineStr">
+      <c r="D237" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E234" s="23" t="inlineStr">
+      <c r="E237" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F234" s="23" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G234" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B235" s="22" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C235" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D235" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E235" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F235" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G235" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="25" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B236" s="26" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="C236" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D236" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E236" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F236" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G236" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="21" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B237" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015-D</t>
-        </is>
-      </c>
-      <c r="C237" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D237" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E237" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F237" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G237" s="21" t="n">
+      <c r="F237" s="23" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G237" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="23" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B238" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C238" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D238" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Clackamas, Hood River</t>
         </is>
       </c>
       <c r="E238" s="23" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F238" s="23" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G238" s="23" t="n">
@@ -10324,38 +10324,38 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="23" t="inlineStr">
+      <c r="A239" s="25" t="inlineStr">
         <is>
           <t>97028</t>
         </is>
       </c>
-      <c r="B239" s="24" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C239" s="24" t="inlineStr">
+      <c r="B239" s="26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C239" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D239" s="24" t="inlineStr">
+      <c r="D239" s="26" t="inlineStr">
         <is>
           <t>Clackamas, Hood River</t>
         </is>
       </c>
-      <c r="E239" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F239" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G239" s="23" t="n">
-        <v>1</v>
+      <c r="E239" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F239" s="25" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G239" s="25" t="n">
+        <v>565</v>
       </c>
     </row>
     <row r="240">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="B240" s="26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C240" s="26" t="inlineStr">
@@ -10386,11 +10386,11 @@
       </c>
       <c r="F240" s="25" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G240" s="25" t="n">
-        <v>565</v>
+        <v>232</v>
       </c>
     </row>
     <row r="241">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B241" s="26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C241" s="26" t="inlineStr">
@@ -10421,116 +10421,116 @@
       </c>
       <c r="F241" s="25" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G241" s="25" t="n">
-        <v>232</v>
+        <v>38</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B242" s="26" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C242" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D242" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E242" s="25" t="inlineStr">
+      <c r="A242" s="23" t="inlineStr">
+        <is>
+          <t>97537</t>
+        </is>
+      </c>
+      <c r="B242" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-JAC-JAC-052</t>
+        </is>
+      </c>
+      <c r="C242" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D242" s="24" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E242" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F242" s="23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G242" s="23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="25" t="inlineStr">
+        <is>
+          <t>97537</t>
+        </is>
+      </c>
+      <c r="B243" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-JAC-ROR-053</t>
+        </is>
+      </c>
+      <c r="C243" s="26" t="inlineStr">
+        <is>
+          <t>Fielders Mountain</t>
+        </is>
+      </c>
+      <c r="D243" s="26" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E243" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F242" s="25" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="G242" s="25" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="23" t="inlineStr">
-        <is>
-          <t>97537</t>
-        </is>
-      </c>
-      <c r="B243" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-JAC-JAC-052</t>
-        </is>
-      </c>
-      <c r="C243" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D243" s="24" t="inlineStr">
-        <is>
-          <t>Jackson</t>
-        </is>
-      </c>
-      <c r="E243" s="23" t="inlineStr">
+      <c r="F243" s="25" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="G243" s="25" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B244" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-070</t>
+        </is>
+      </c>
+      <c r="C244" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D244" s="24" t="inlineStr">
+        <is>
+          <t>Wheeler</t>
+        </is>
+      </c>
+      <c r="E244" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F243" s="23" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G243" s="23" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="25" t="inlineStr">
-        <is>
-          <t>97537</t>
-        </is>
-      </c>
-      <c r="B244" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-JAC-ROR-053</t>
-        </is>
-      </c>
-      <c r="C244" s="26" t="inlineStr">
-        <is>
-          <t>Fielders Mountain</t>
-        </is>
-      </c>
-      <c r="D244" s="26" t="inlineStr">
-        <is>
-          <t>Jackson</t>
-        </is>
-      </c>
-      <c r="E244" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F244" s="25" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="G244" s="25" t="n">
-        <v>307</v>
+      <c r="F244" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G244" s="23" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="245">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="B245" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-070</t>
+          <t>US-OR-WHE-WHH-068</t>
         </is>
       </c>
       <c r="C245" s="24" t="inlineStr">
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="G245" s="23" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="246">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="B246" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-068</t>
+          <t>US-OR-WHE-WHH-072-A</t>
         </is>
       </c>
       <c r="C246" s="24" t="inlineStr">
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="G246" s="23" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="247">
@@ -10611,12 +10611,12 @@
       </c>
       <c r="B247" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-072-A</t>
+          <t>US-OR-WHE-WHH-034-A</t>
         </is>
       </c>
       <c r="C247" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D247" s="24" t="inlineStr">
@@ -10631,11 +10631,11 @@
       </c>
       <c r="F247" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G247" s="23" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="B248" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-034-A</t>
+          <t>US-OR-WHE-WHH-072-C</t>
         </is>
       </c>
       <c r="C248" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D248" s="24" t="inlineStr">
@@ -10666,11 +10666,11 @@
       </c>
       <c r="F248" s="23" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="G248" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="B249" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-072-C</t>
+          <t>US-OR-WHE-WHH-090-A</t>
         </is>
       </c>
       <c r="C249" s="24" t="inlineStr">
@@ -10701,46 +10701,46 @@
       </c>
       <c r="F249" s="23" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G249" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="23" t="inlineStr">
+      <c r="A250" s="25" t="inlineStr">
         <is>
           <t>97750</t>
         </is>
       </c>
-      <c r="B250" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-090-A</t>
-        </is>
-      </c>
-      <c r="C250" s="24" t="inlineStr">
+      <c r="B250" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-MIT-076</t>
+        </is>
+      </c>
+      <c r="C250" s="26" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D250" s="24" t="inlineStr">
+      <c r="D250" s="26" t="inlineStr">
         <is>
           <t>Wheeler</t>
         </is>
       </c>
-      <c r="E250" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F250" s="23" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G250" s="23" t="n">
-        <v>1</v>
+      <c r="E250" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F250" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G250" s="25" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="251">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="B251" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-MIT-076</t>
+          <t>US-OR-WHE-WHH-062</t>
         </is>
       </c>
       <c r="C251" s="26" t="inlineStr">
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="G251" s="25" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
     </row>
     <row r="252">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="B252" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-062</t>
+          <t>US-OR-WHE-WHH-060-A</t>
         </is>
       </c>
       <c r="C252" s="26" t="inlineStr">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G252" s="25" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="253">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="B253" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-060-A</t>
+          <t>US-OR-WHE-WHH-060-B</t>
         </is>
       </c>
       <c r="C253" s="26" t="inlineStr">
@@ -10841,11 +10841,11 @@
       </c>
       <c r="F253" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="G253" s="25" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B254" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-060-B</t>
+          <t>US-OR-WHE-WHH-054</t>
         </is>
       </c>
       <c r="C254" s="26" t="inlineStr">
@@ -10876,11 +10876,11 @@
       </c>
       <c r="F254" s="25" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="G254" s="25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="B255" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-054</t>
+          <t>US-OR-WHE-MIT-074</t>
         </is>
       </c>
       <c r="C255" s="26" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="F255" s="25" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G255" s="25" t="n">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B256" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-MIT-074</t>
+          <t>US-OR-WHE-MIT-078</t>
         </is>
       </c>
       <c r="C256" s="26" t="inlineStr">
@@ -10950,41 +10950,41 @@
         </is>
       </c>
       <c r="G256" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="25" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B257" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-MIT-078</t>
-        </is>
-      </c>
-      <c r="C257" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D257" s="26" t="inlineStr">
-        <is>
-          <t>Wheeler</t>
-        </is>
-      </c>
-      <c r="E257" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F257" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G257" s="25" t="n">
+      <c r="A257" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B257" s="24" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C257" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D257" s="24" t="inlineStr">
+        <is>
+          <t>Clackamas, Hood River</t>
+        </is>
+      </c>
+      <c r="E257" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F257" s="23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G257" s="23" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="B258" s="24" t="inlineStr">
         <is>
-          <t>Elk Mountain</t>
+          <t>Mill Creek Buttes</t>
         </is>
       </c>
       <c r="C258" s="24" t="inlineStr">
@@ -11016,11 +11016,11 @@
       </c>
       <c r="F258" s="23" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G258" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B259" s="24" t="inlineStr">
         <is>
-          <t>Mill Creek Buttes</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C259" s="24" t="inlineStr">
@@ -11051,46 +11051,46 @@
       </c>
       <c r="F259" s="23" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G259" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="23" t="inlineStr">
+      <c r="A260" s="25" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B260" s="24" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C260" s="24" t="inlineStr">
+      <c r="B260" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur North</t>
+        </is>
+      </c>
+      <c r="C260" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D260" s="24" t="inlineStr">
+      <c r="D260" s="26" t="inlineStr">
         <is>
           <t>Clackamas, Hood River</t>
         </is>
       </c>
-      <c r="E260" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F260" s="23" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="G260" s="23" t="n">
-        <v>1</v>
+      <c r="E260" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F260" s="25" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G260" s="25" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="261">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="B261" s="26" t="inlineStr">
         <is>
-          <t>Cooper Spur North</t>
+          <t>Cooper Spur South</t>
         </is>
       </c>
       <c r="C261" s="26" t="inlineStr">
@@ -11121,11 +11121,11 @@
       </c>
       <c r="F261" s="25" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G261" s="25" t="n">
-        <v>158</v>
+        <v>63</v>
       </c>
     </row>
     <row r="262">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="B262" s="26" t="inlineStr">
         <is>
-          <t>Cooper Spur South</t>
+          <t>Gibson Prairie</t>
         </is>
       </c>
       <c r="C262" s="26" t="inlineStr">
@@ -11156,11 +11156,11 @@
       </c>
       <c r="F262" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G262" s="25" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B263" s="26" t="inlineStr">
         <is>
-          <t>Gibson Prairie</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C263" s="26" t="inlineStr">
@@ -11191,46 +11191,46 @@
       </c>
       <c r="F263" s="25" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G263" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B264" s="26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C264" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D264" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E264" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F264" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G264" s="25" t="n">
-        <v>1</v>
+      <c r="A264" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B264" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C264" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D264" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E264" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F264" s="23" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G264" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="265">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="B265" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1435</t>
+          <t>US-OR-UNI-UCO-1450</t>
         </is>
       </c>
       <c r="C265" s="24" t="inlineStr">
@@ -11261,46 +11261,46 @@
       </c>
       <c r="F265" s="23" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G265" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="23" t="inlineStr">
+      <c r="A266" s="25" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B266" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C266" s="24" t="inlineStr">
+      <c r="B266" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1421</t>
+        </is>
+      </c>
+      <c r="C266" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D266" s="24" t="inlineStr">
+      <c r="D266" s="26" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E266" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F266" s="23" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G266" s="23" t="n">
-        <v>1</v>
+      <c r="E266" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F266" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G266" s="25" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="267">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B267" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-UNI-UCO-1436</t>
         </is>
       </c>
       <c r="C267" s="26" t="inlineStr">
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="G267" s="25" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="268">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B268" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1436</t>
+          <t>US-OR-UNI-UCO-1437</t>
         </is>
       </c>
       <c r="C268" s="26" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="B269" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C269" s="26" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="F269" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G269" s="25" t="n">
@@ -11409,73 +11409,73 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="25" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B270" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1438</t>
-        </is>
-      </c>
-      <c r="C270" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D270" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E270" s="25" t="inlineStr">
+      <c r="A270" s="23" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B270" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1941</t>
+        </is>
+      </c>
+      <c r="C270" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D270" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E270" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F270" s="23" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G270" s="23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="25" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B271" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2261</t>
+        </is>
+      </c>
+      <c r="C271" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D271" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E271" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F270" s="25" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G270" s="25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="23" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B271" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C271" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D271" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E271" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F271" s="23" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="G271" s="23" t="n">
-        <v>15</v>
+      <c r="F271" s="25" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G271" s="25" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="272">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B272" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-KLA-KLA-1936</t>
         </is>
       </c>
       <c r="C272" s="26" t="inlineStr">
@@ -11506,11 +11506,11 @@
       </c>
       <c r="F272" s="25" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G272" s="25" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="B273" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1936</t>
+          <t>US-OR-KLA-KLA-2256</t>
         </is>
       </c>
       <c r="C273" s="26" t="inlineStr">
@@ -11541,11 +11541,11 @@
       </c>
       <c r="F273" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G273" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="B274" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2256</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C274" s="26" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="F274" s="25" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G274" s="25" t="n">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="B275" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1931</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C275" s="26" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F275" s="25" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G275" s="25" t="n">
@@ -11619,108 +11619,108 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B276" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1701</t>
-        </is>
-      </c>
-      <c r="C276" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D276" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E276" s="25" t="inlineStr">
+      <c r="A276" s="23" t="inlineStr">
+        <is>
+          <t>97848</t>
+        </is>
+      </c>
+      <c r="B276" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-052-C</t>
+        </is>
+      </c>
+      <c r="C276" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D276" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E276" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F276" s="23" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G276" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="25" t="inlineStr">
+        <is>
+          <t>97848</t>
+        </is>
+      </c>
+      <c r="B277" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-023</t>
+        </is>
+      </c>
+      <c r="C277" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D277" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E277" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F276" s="25" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="G276" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="23" t="inlineStr">
-        <is>
-          <t>97848</t>
-        </is>
-      </c>
-      <c r="B277" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-052-C</t>
-        </is>
-      </c>
-      <c r="C277" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D277" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E277" s="23" t="inlineStr">
+      <c r="F277" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G277" s="25" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="23" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B278" s="24" t="inlineStr">
+        <is>
+          <t>Salmon_3b</t>
+        </is>
+      </c>
+      <c r="C278" s="24" t="inlineStr">
+        <is>
+          <t>Salmon</t>
+        </is>
+      </c>
+      <c r="D278" s="24" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E278" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F277" s="23" t="inlineStr">
-        <is>
-          <t>17%</t>
-        </is>
-      </c>
-      <c r="G277" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="25" t="inlineStr">
-        <is>
-          <t>97848</t>
-        </is>
-      </c>
-      <c r="B278" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-023</t>
-        </is>
-      </c>
-      <c r="C278" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D278" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E278" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F278" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G278" s="25" t="n">
-        <v>47</v>
+      <c r="F278" s="23" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G278" s="23" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="279">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="B279" s="24" t="inlineStr">
         <is>
-          <t>Salmon_3b</t>
+          <t>Olive_9</t>
         </is>
       </c>
       <c r="C279" s="24" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Salmon/Olive Butte Fires</t>
         </is>
       </c>
       <c r="D279" s="24" t="inlineStr">
@@ -11751,11 +11751,11 @@
       </c>
       <c r="F279" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G279" s="23" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="B280" s="24" t="inlineStr">
         <is>
-          <t>Olive_9</t>
+          <t>Olive_3</t>
         </is>
       </c>
       <c r="C280" s="24" t="inlineStr">
@@ -11790,7 +11790,7 @@
         </is>
       </c>
       <c r="G280" s="23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="B281" s="24" t="inlineStr">
         <is>
-          <t>Olive_3</t>
+          <t>Olive_7</t>
         </is>
       </c>
       <c r="C281" s="24" t="inlineStr">
@@ -11821,11 +11821,11 @@
       </c>
       <c r="F281" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="G281" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="B282" s="24" t="inlineStr">
         <is>
-          <t>Olive_7</t>
+          <t>Olive_12</t>
         </is>
       </c>
       <c r="C282" s="24" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="F282" s="23" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G282" s="23" t="n">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="B283" s="24" t="inlineStr">
         <is>
-          <t>Olive_12</t>
+          <t>Salmon 12</t>
         </is>
       </c>
       <c r="C283" s="24" t="inlineStr">
@@ -11891,11 +11891,11 @@
       </c>
       <c r="F283" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G283" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="B284" s="24" t="inlineStr">
         <is>
-          <t>Salmon 12</t>
+          <t>Olive_5</t>
         </is>
       </c>
       <c r="C284" s="24" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="F284" s="23" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G284" s="23" t="n">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="B285" s="24" t="inlineStr">
         <is>
-          <t>Olive_5</t>
+          <t>Salmon_8</t>
         </is>
       </c>
       <c r="C285" s="24" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="F285" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G285" s="23" t="n">
@@ -11971,22 +11971,22 @@
     <row r="286">
       <c r="A286" s="23" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97907</t>
         </is>
       </c>
       <c r="B286" s="24" t="inlineStr">
         <is>
-          <t>Salmon_8</t>
+          <t>US-OR-BAK-BAB-1410-A</t>
         </is>
       </c>
       <c r="C286" s="24" t="inlineStr">
         <is>
-          <t>Salmon/Olive Butte Fires</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D286" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E286" s="23" t="inlineStr">
@@ -11996,11 +11996,11 @@
       </c>
       <c r="F286" s="23" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G286" s="23" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="287">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B287" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1410-A</t>
+          <t>US-OR-BAK-BAB-1412-A</t>
         </is>
       </c>
       <c r="C287" s="24" t="inlineStr">
@@ -12031,11 +12031,11 @@
       </c>
       <c r="F287" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G287" s="23" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="B288" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1412-A</t>
+          <t>US-OR-BAK-BAB-1408-A</t>
         </is>
       </c>
       <c r="C288" s="24" t="inlineStr">
@@ -12066,11 +12066,11 @@
       </c>
       <c r="F288" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G288" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B289" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1408-A</t>
+          <t>US-OR-BAK-RCH-572</t>
         </is>
       </c>
       <c r="C289" s="24" t="inlineStr">
@@ -12101,11 +12101,11 @@
       </c>
       <c r="F289" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G289" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B290" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-RCH-572</t>
+          <t>US-OR-BAK-RCH-570</t>
         </is>
       </c>
       <c r="C290" s="24" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="F290" s="23" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G290" s="23" t="n">
@@ -12144,38 +12144,38 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="23" t="inlineStr">
+      <c r="A291" s="25" t="inlineStr">
         <is>
           <t>97907</t>
         </is>
       </c>
-      <c r="B291" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-RCH-570</t>
-        </is>
-      </c>
-      <c r="C291" s="24" t="inlineStr">
+      <c r="B291" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1414-A</t>
+        </is>
+      </c>
+      <c r="C291" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D291" s="24" t="inlineStr">
+      <c r="D291" s="26" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E291" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F291" s="23" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G291" s="23" t="n">
-        <v>1</v>
+      <c r="E291" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F291" s="25" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G291" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="B292" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1414-A</t>
+          <t>US-OR-BAK-HUN-319</t>
         </is>
       </c>
       <c r="C292" s="26" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="F292" s="25" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G292" s="25" t="n">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="B293" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-HUN-319</t>
+          <t>US-OR-BAK-BAB-1528</t>
         </is>
       </c>
       <c r="C293" s="26" t="inlineStr">
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G293" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="B294" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1528</t>
+          <t>US-OR-BAK-BAB-1416-A</t>
         </is>
       </c>
       <c r="C294" s="26" t="inlineStr">
@@ -12276,46 +12276,46 @@
       </c>
       <c r="F294" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G294" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="23" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="B295" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1572</t>
+        </is>
+      </c>
+      <c r="C295" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D295" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E295" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F295" s="23" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G295" s="23" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="25" t="inlineStr">
-        <is>
-          <t>97907</t>
-        </is>
-      </c>
-      <c r="B295" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1416-A</t>
-        </is>
-      </c>
-      <c r="C295" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D295" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E295" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F295" s="25" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="G295" s="25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="B296" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C296" s="24" t="inlineStr">
@@ -12346,46 +12346,46 @@
       </c>
       <c r="F296" s="23" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G296" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="23" t="inlineStr">
+      <c r="A297" s="25" t="inlineStr">
         <is>
           <t>97621</t>
         </is>
       </c>
-      <c r="B297" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1566</t>
-        </is>
-      </c>
-      <c r="C297" s="24" t="inlineStr">
+      <c r="B297" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1472</t>
+        </is>
+      </c>
+      <c r="C297" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D297" s="24" t="inlineStr">
+      <c r="D297" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E297" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F297" s="23" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G297" s="23" t="n">
-        <v>1</v>
+      <c r="E297" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F297" s="25" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="G297" s="25" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="298">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="B298" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1472</t>
+          <t>US-OR-KLA-FHZ-1584-A</t>
         </is>
       </c>
       <c r="C298" s="26" t="inlineStr">
@@ -12416,11 +12416,11 @@
       </c>
       <c r="F298" s="25" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G298" s="25" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="B299" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1584-A</t>
+          <t>US-OR-KLA-KLA-1452</t>
         </is>
       </c>
       <c r="C299" s="26" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="F299" s="25" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G299" s="25" t="n">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="B300" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1452</t>
+          <t>US-OR-KLA-FHZ-1585</t>
         </is>
       </c>
       <c r="C300" s="26" t="inlineStr">
@@ -12486,11 +12486,11 @@
       </c>
       <c r="F300" s="25" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G300" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="B301" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1585</t>
+          <t>US-OR-KLA-FHZ-1584-B</t>
         </is>
       </c>
       <c r="C301" s="26" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F301" s="25" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G301" s="25" t="n">
@@ -12529,73 +12529,73 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="25" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="B302" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1584-B</t>
-        </is>
-      </c>
-      <c r="C302" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D302" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E302" s="25" t="inlineStr">
+      <c r="A302" s="23" t="inlineStr">
+        <is>
+          <t>97905</t>
+        </is>
+      </c>
+      <c r="B302" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1412-A</t>
+        </is>
+      </c>
+      <c r="C302" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D302" s="24" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E302" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F302" s="23" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G302" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="25" t="inlineStr">
+        <is>
+          <t>97905</t>
+        </is>
+      </c>
+      <c r="B303" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1406-B</t>
+        </is>
+      </c>
+      <c r="C303" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D303" s="26" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E303" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F302" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G302" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="23" t="inlineStr">
-        <is>
-          <t>97905</t>
-        </is>
-      </c>
-      <c r="B303" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1412-A</t>
-        </is>
-      </c>
-      <c r="C303" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D303" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E303" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F303" s="23" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G303" s="23" t="n">
-        <v>1</v>
+      <c r="F303" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G303" s="25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="B304" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1406-B</t>
+          <t>US-OR-BAK-BAB-1416-A</t>
         </is>
       </c>
       <c r="C304" s="26" t="inlineStr">
@@ -12626,11 +12626,11 @@
       </c>
       <c r="F304" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="G304" s="25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="B305" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1416-A</t>
+          <t>US-OR-BAK-BAB-1418-A</t>
         </is>
       </c>
       <c r="C305" s="26" t="inlineStr">
@@ -12661,11 +12661,11 @@
       </c>
       <c r="F305" s="25" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G305" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B306" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1418-A</t>
+          <t>US-OR-BAK-BAB-1414-A</t>
         </is>
       </c>
       <c r="C306" s="26" t="inlineStr">
@@ -12696,46 +12696,46 @@
       </c>
       <c r="F306" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G306" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="25" t="inlineStr">
-        <is>
-          <t>97905</t>
-        </is>
-      </c>
-      <c r="B307" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1414-A</t>
-        </is>
-      </c>
-      <c r="C307" s="26" t="inlineStr">
+      <c r="A307" s="23" t="inlineStr">
+        <is>
+          <t>97830</t>
+        </is>
+      </c>
+      <c r="B307" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-036-B</t>
+        </is>
+      </c>
+      <c r="C307" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D307" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E307" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F307" s="25" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="G307" s="25" t="n">
-        <v>1</v>
+      <c r="D307" s="24" t="inlineStr">
+        <is>
+          <t>Wheeler</t>
+        </is>
+      </c>
+      <c r="E307" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F307" s="23" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="G307" s="23" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="308">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="B308" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-036-B</t>
+          <t>US-OR-WHE-WHH-034-A</t>
         </is>
       </c>
       <c r="C308" s="24" t="inlineStr">
@@ -12766,22 +12766,22 @@
       </c>
       <c r="F308" s="23" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G308" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="23" t="inlineStr">
         <is>
-          <t>97830</t>
+          <t>97526</t>
         </is>
       </c>
       <c r="B309" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-034-A</t>
+          <t>US-OR-JAC-JAC-052</t>
         </is>
       </c>
       <c r="C309" s="24" t="inlineStr">
@@ -12791,91 +12791,91 @@
       </c>
       <c r="D309" s="24" t="inlineStr">
         <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E309" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F309" s="23" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="G309" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="25" t="inlineStr">
+        <is>
+          <t>97526</t>
+        </is>
+      </c>
+      <c r="B310" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-JAC-ROR-053</t>
+        </is>
+      </c>
+      <c r="C310" s="26" t="inlineStr">
+        <is>
+          <t>Fielders Mountain</t>
+        </is>
+      </c>
+      <c r="D310" s="26" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E310" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F310" s="25" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="G310" s="25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="23" t="inlineStr">
+        <is>
+          <t>97874</t>
+        </is>
+      </c>
+      <c r="B311" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-052-C</t>
+        </is>
+      </c>
+      <c r="C311" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D311" s="24" t="inlineStr">
+        <is>
           <t>Wheeler</t>
         </is>
       </c>
-      <c r="E309" s="23" t="inlineStr">
+      <c r="E311" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F309" s="23" t="inlineStr">
-        <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="G309" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="23" t="inlineStr">
-        <is>
-          <t>97526</t>
-        </is>
-      </c>
-      <c r="B310" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-JAC-JAC-052</t>
-        </is>
-      </c>
-      <c r="C310" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D310" s="24" t="inlineStr">
-        <is>
-          <t>Jackson</t>
-        </is>
-      </c>
-      <c r="E310" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F310" s="23" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="G310" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="25" t="inlineStr">
-        <is>
-          <t>97526</t>
-        </is>
-      </c>
-      <c r="B311" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-JAC-ROR-053</t>
-        </is>
-      </c>
-      <c r="C311" s="26" t="inlineStr">
-        <is>
-          <t>Fielders Mountain</t>
-        </is>
-      </c>
-      <c r="D311" s="26" t="inlineStr">
-        <is>
-          <t>Jackson</t>
-        </is>
-      </c>
-      <c r="E311" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F311" s="25" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G311" s="25" t="n">
-        <v>11</v>
+      <c r="F311" s="23" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="G311" s="23" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="312">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="B312" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-052-C</t>
+          <t>US-OR-WHE-WHH-036-B</t>
         </is>
       </c>
       <c r="C312" s="24" t="inlineStr">
@@ -12906,11 +12906,11 @@
       </c>
       <c r="F312" s="23" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G312" s="23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="B313" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-036-B</t>
+          <t>US-OR-WHE-WHH-034-A</t>
         </is>
       </c>
       <c r="C313" s="24" t="inlineStr">
@@ -12949,73 +12949,73 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="23" t="inlineStr">
+      <c r="A314" s="25" t="inlineStr">
         <is>
           <t>97874</t>
         </is>
       </c>
-      <c r="B314" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-034-A</t>
-        </is>
-      </c>
-      <c r="C314" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D314" s="24" t="inlineStr">
+      <c r="B314" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-054</t>
+        </is>
+      </c>
+      <c r="C314" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D314" s="26" t="inlineStr">
         <is>
           <t>Wheeler</t>
         </is>
       </c>
-      <c r="E314" s="23" t="inlineStr">
+      <c r="E314" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F314" s="25" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G314" s="25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="23" t="inlineStr">
+        <is>
+          <t>97817</t>
+        </is>
+      </c>
+      <c r="B315" s="24" t="inlineStr">
+        <is>
+          <t>Salmon 12</t>
+        </is>
+      </c>
+      <c r="C315" s="24" t="inlineStr">
+        <is>
+          <t>Salmon/Olive Butte Fires</t>
+        </is>
+      </c>
+      <c r="D315" s="24" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E315" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F314" s="23" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G314" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="25" t="inlineStr">
-        <is>
-          <t>97874</t>
-        </is>
-      </c>
-      <c r="B315" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-054</t>
-        </is>
-      </c>
-      <c r="C315" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D315" s="26" t="inlineStr">
-        <is>
-          <t>Wheeler</t>
-        </is>
-      </c>
-      <c r="E315" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F315" s="25" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="G315" s="25" t="n">
-        <v>4</v>
+      <c r="F315" s="23" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="G315" s="23" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="316">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B316" s="24" t="inlineStr">
         <is>
-          <t>Salmon 12</t>
+          <t>Olive_7</t>
         </is>
       </c>
       <c r="C316" s="24" t="inlineStr">
@@ -13046,11 +13046,11 @@
       </c>
       <c r="F316" s="23" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="G316" s="23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="B317" s="24" t="inlineStr">
         <is>
-          <t>Olive_7</t>
+          <t>Salmon_8</t>
         </is>
       </c>
       <c r="C317" s="24" t="inlineStr">
@@ -13081,11 +13081,11 @@
       </c>
       <c r="F317" s="23" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G317" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="B318" s="24" t="inlineStr">
         <is>
-          <t>Salmon_8</t>
+          <t>Salmon_3b</t>
         </is>
       </c>
       <c r="C318" s="24" t="inlineStr">
         <is>
-          <t>Salmon/Olive Butte Fires</t>
+          <t>Salmon</t>
         </is>
       </c>
       <c r="D318" s="24" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="F318" s="23" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G318" s="23" t="n">
@@ -13126,22 +13126,22 @@
     <row r="319">
       <c r="A319" s="23" t="inlineStr">
         <is>
-          <t>97817</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="B319" s="24" t="inlineStr">
         <is>
-          <t>Salmon_3b</t>
+          <t>US-OR-UMA-UMC-1406043-C</t>
         </is>
       </c>
       <c r="C319" s="24" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D319" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E319" s="23" t="inlineStr">
@@ -13151,32 +13151,32 @@
       </c>
       <c r="F319" s="23" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G319" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="23" t="inlineStr">
         <is>
-          <t>99362</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B320" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C320" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D320" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E320" s="23" t="inlineStr">
@@ -13186,46 +13186,46 @@
       </c>
       <c r="F320" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G320" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="23" t="inlineStr">
+      <c r="A321" s="25" t="inlineStr">
         <is>
           <t>97037</t>
         </is>
       </c>
-      <c r="B321" s="24" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="C321" s="24" t="inlineStr">
+      <c r="B321" s="26" t="inlineStr">
+        <is>
+          <t>KM</t>
+        </is>
+      </c>
+      <c r="C321" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D321" s="24" t="inlineStr">
+      <c r="D321" s="26" t="inlineStr">
         <is>
           <t>Wasco</t>
         </is>
       </c>
-      <c r="E321" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F321" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G321" s="23" t="n">
-        <v>1</v>
+      <c r="E321" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F321" s="25" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="G321" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B322" s="26" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="C322" s="26" t="inlineStr">
@@ -13256,45 +13256,45 @@
       </c>
       <c r="F322" s="25" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G322" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="25" t="inlineStr">
-        <is>
-          <t>97037</t>
-        </is>
-      </c>
-      <c r="B323" s="26" t="inlineStr">
-        <is>
-          <t>SBR</t>
-        </is>
-      </c>
-      <c r="C323" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D323" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E323" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F323" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G323" s="25" t="n">
+      <c r="A323" s="23" t="inlineStr">
+        <is>
+          <t>97870</t>
+        </is>
+      </c>
+      <c r="B323" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-RCH-572</t>
+        </is>
+      </c>
+      <c r="C323" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D323" s="24" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E323" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F323" s="23" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G323" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="B324" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-RCH-572</t>
+          <t>US-OR-BAK-RCH-570</t>
         </is>
       </c>
       <c r="C324" s="24" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="F324" s="23" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G324" s="23" t="n">
@@ -13336,7 +13336,7 @@
     <row r="325">
       <c r="A325" s="23" t="inlineStr">
         <is>
-          <t>97870</t>
+          <t>97840</t>
         </is>
       </c>
       <c r="B325" s="24" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="F325" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G325" s="23" t="n">
@@ -13369,38 +13369,38 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="23" t="inlineStr">
-        <is>
-          <t>97840</t>
-        </is>
-      </c>
-      <c r="B326" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-RCH-570</t>
-        </is>
-      </c>
-      <c r="C326" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D326" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E326" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F326" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G326" s="23" t="n">
-        <v>1</v>
+      <c r="A326" s="25" t="inlineStr">
+        <is>
+          <t>97049</t>
+        </is>
+      </c>
+      <c r="B326" s="26" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C326" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D326" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E326" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F326" s="25" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="G326" s="25" t="n">
+        <v>403</v>
       </c>
     </row>
     <row r="327">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="B327" s="26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C327" s="26" t="inlineStr">
@@ -13431,11 +13431,11 @@
       </c>
       <c r="F327" s="25" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G327" s="25" t="n">
-        <v>403</v>
+        <v>186</v>
       </c>
     </row>
     <row r="328">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B328" s="26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C328" s="26" t="inlineStr">
@@ -13466,32 +13466,32 @@
       </c>
       <c r="F328" s="25" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G328" s="25" t="n">
-        <v>186</v>
+        <v>88</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="25" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97833</t>
         </is>
       </c>
       <c r="B329" s="26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C329" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Anthony Fire</t>
         </is>
       </c>
       <c r="D329" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E329" s="25" t="inlineStr">
@@ -13501,32 +13501,32 @@
       </c>
       <c r="F329" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G329" s="25" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="25" t="inlineStr">
         <is>
-          <t>97833</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="B330" s="26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>BC1</t>
         </is>
       </c>
       <c r="C330" s="26" t="inlineStr">
         <is>
-          <t>Anthony Fire</t>
+          <t>Burnt Creek Fire</t>
         </is>
       </c>
       <c r="D330" s="26" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Wallowa</t>
         </is>
       </c>
       <c r="E330" s="25" t="inlineStr">
@@ -13536,32 +13536,32 @@
       </c>
       <c r="F330" s="25" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="G330" s="25" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="25" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="B331" s="26" t="inlineStr">
         <is>
-          <t>BC1</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C331" s="26" t="inlineStr">
         <is>
-          <t>Burnt Creek Fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D331" s="26" t="inlineStr">
         <is>
-          <t>Wallowa</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E331" s="25" t="inlineStr">
@@ -13571,32 +13571,32 @@
       </c>
       <c r="F331" s="25" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G331" s="25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="25" t="inlineStr">
         <is>
-          <t>97067</t>
+          <t>97864</t>
         </is>
       </c>
       <c r="B332" s="26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>US-OR-GRA-GRN-023</t>
         </is>
       </c>
       <c r="C332" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D332" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E332" s="25" t="inlineStr">
@@ -13616,22 +13616,22 @@
     <row r="333">
       <c r="A333" s="25" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="B333" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-023</t>
+          <t>LDWT</t>
         </is>
       </c>
       <c r="C333" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D333" s="26" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E333" s="25" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="F333" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G333" s="25" t="n">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="B334" s="26" t="inlineStr">
         <is>
-          <t>LDWT</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="C334" s="26" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="F334" s="25" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G334" s="25" t="n">
@@ -13686,12 +13686,12 @@
     <row r="335">
       <c r="A335" s="25" t="inlineStr">
         <is>
-          <t>97029</t>
+          <t>97040</t>
         </is>
       </c>
       <c r="B335" s="26" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="C335" s="26" t="inlineStr">
@@ -13721,22 +13721,22 @@
     <row r="336">
       <c r="A336" s="25" t="inlineStr">
         <is>
-          <t>97040</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="B336" s="26" t="inlineStr">
         <is>
-          <t>MCR</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C336" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D336" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E336" s="25" t="inlineStr">
@@ -13753,43 +13753,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" s="25" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="B337" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C337" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D337" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E337" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F337" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G337" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="339" ht="60" customHeight="1">
-      <c r="A339" s="27" t="inlineStr">
+    <row r="338" ht="60" customHeight="1">
+      <c r="A338" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -13797,7 +13762,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A339:G339"/>
+    <mergeCell ref="A338:G338"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
